--- a/output/pdf_financials_xlsx/PER.xlsx
+++ b/output/pdf_financials_xlsx/PER.xlsx
@@ -1303,19 +1303,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>6.268738</v>
+        <v>-6.268738</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.414226</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.349577</v>
+        <v>0.005625</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>15.864215</v>
+        <v>-0.005625</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9.704155999999999</v>
+        <v>0.24</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0.1376</v>
@@ -1327,10 +1327,10 @@
         <v>2.798271</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.453297</v>
+        <v>-2.453297</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.7706</v>
+        <v>-1.7706</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-1.367827</v>
@@ -1382,7 +1382,7 @@
         <v>-0.0105</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.1296</v>
+        <v>-5.466942</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6.268738</v>
+        <v>-6.268738</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.207113</v>
+        <v>-1.207113</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.671976</v>
+        <v>-2.671976</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7.93492</v>
+        <v>-7.93492</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4.732078</v>
+        <v>-4.732078</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-2.254702</v>
@@ -1624,13 +1624,13 @@
         <v>-5.140889</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.668671</v>
+        <v>-2.668671</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.453297</v>
+        <v>-2.453297</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.7706</v>
+        <v>-1.7706</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-1.367827</v>
@@ -1777,19 +1777,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6.268738</v>
+        <v>-6.268738</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.207113</v>
+        <v>-1.207113</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.671976</v>
+        <v>-2.671976</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7.93492</v>
+        <v>-7.93492</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.732078</v>
+        <v>-4.732078</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-2.254702</v>
@@ -1798,13 +1798,13 @@
         <v>-5.140889</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.668671</v>
+        <v>-2.668671</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.453297</v>
+        <v>-2.453297</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.7706</v>
+        <v>-1.7706</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-1.367827</v>
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>69.652644</v>
+        <v>-69.652644</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>60.35565</v>
+        <v>-60.35565</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>133.5988</v>
+        <v>-133.5988</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>198.373</v>
+        <v>-198.373</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>236.6039</v>
+        <v>-236.6039</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1974,13 +1974,13 @@
         <v>257.04445</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>33.358388</v>
+        <v>-33.358388</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>40.888283</v>
+        <v>-40.888283</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>59.02</v>
+        <v>-59.02</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>68.39135</v>
@@ -2019,19 +2019,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6.268738</v>
+        <v>-6.268738</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.414226</v>
+        <v>0</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.349577</v>
+        <v>0.005625</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15.864215</v>
+        <v>-0.005625</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>9.704155999999999</v>
+        <v>0.24</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0.1376</v>
@@ -2043,10 +2043,10 @@
         <v>2.798271</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.453297</v>
+        <v>-2.453297</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.7706</v>
+        <v>-1.7706</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-1.367827</v>
@@ -2135,19 +2135,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.268738</v>
+        <v>-6.268738</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.414226</v>
+        <v>0</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.349577</v>
+        <v>0.005625</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>15.864215</v>
+        <v>-0.005625</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9.704155999999999</v>
+        <v>0.24</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.1376</v>
@@ -2159,10 +2159,10 @@
         <v>2.798271</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.453297</v>
+        <v>-2.453297</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.7706</v>
+        <v>-1.7706</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-1.367827</v>
@@ -2285,19 +2285,21 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>50</v>
+        <v>-0</v>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>50.05257425026315</v>
+        <v>47601.79555555555</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>49.98227142030034</v>
+        <v>-140965.2444444445</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>51.23658358336366</v>
+        <v>2071.699166666666</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>1738.591569767442</v>
@@ -2306,13 +2308,13 @@
         <v>-0.2046628433048644</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>4.631431337422287</v>
+        <v>195.3685686625777</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -5924,49 +5926,49 @@
         <v>3.752639</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>4.412312</v>
+        <v>1.612647</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.512456</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.069561</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.484819</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.931001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.390079</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.823275</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.741567</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.30636</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.302492</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.177151</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.177151</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.321881</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.27375</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.212644</v>
       </c>
     </row>
     <row r="93">
@@ -6277,10 +6279,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>6.268738</v>
+        <v>-6.268738</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>1.207113</v>
+        <v>-1.207113</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-2.671976</v>
@@ -10158,7 +10160,11 @@
           <t>WARRANT RESERVE (Note 12(b))</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -10251,7 +10257,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 13)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -13521,7 +13531,11 @@
           <t>WARRANT RESERVE (Note 12(b)) 23,340</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -13622,7 +13636,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 13) 298,541</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -16207,7 +16225,11 @@
           <t>WARRANT RESERVE (Note 13(b)) 23,720</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -16308,7 +16330,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 14) 347,753</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -21679,7 +21705,11 @@
           <t>WARRANT RESERVE (Note 13(b))</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -21778,7 +21808,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 14)</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -23683,7 +23717,11 @@
           <t>WARRANT RESERVE (Note 10(b))</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -23782,7 +23820,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 11)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -24390,7 +24432,11 @@
           <t>WARRANT RESERVE (Note 10(b))</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -24491,7 +24537,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 11)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -25687,7 +25737,11 @@
           <t>WARRANT RESERVE (Note 11(b))</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -25786,7 +25840,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 12)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -26378,7 +26436,11 @@
           <t>WARRANT RESERVE (Note 9(b))</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -26475,7 +26537,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 10)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -28115,7 +28181,11 @@
           <t>WARRANT RESERVE (Note 9) 1,437,911</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -28214,7 +28284,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 10) 2,074,545</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -33229,7 +33303,7 @@
         <v>-0.10063</v>
       </c>
       <c r="T247" s="5" t="n">
-        <v>0.043973</v>
+        <v>-0.043973</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
@@ -63853,10 +63927,10 @@
         </is>
       </c>
       <c r="L553" s="5" t="n">
-        <v>2.643671</v>
+        <v>-2.643671</v>
       </c>
       <c r="M553" s="5" t="n">
-        <v>2.465603</v>
+        <v>-2.465603</v>
       </c>
       <c r="N553" t="inlineStr">
         <is>
@@ -68314,19 +68388,19 @@
         </is>
       </c>
       <c r="F598" s="5" t="n">
-        <v>1.207113</v>
+        <v>-1.207113</v>
       </c>
       <c r="G598" s="5" t="n">
-        <v>2.671976</v>
+        <v>-2.671976</v>
       </c>
       <c r="H598" s="5" t="n">
-        <v>7.93492</v>
+        <v>-7.93492</v>
       </c>
       <c r="I598" s="5" t="n">
-        <v>4.732078</v>
+        <v>-4.732078</v>
       </c>
       <c r="J598" s="5" t="n">
-        <v>2.254702</v>
+        <v>-2.254702</v>
       </c>
       <c r="K598" t="inlineStr">
         <is>
@@ -68339,7 +68413,7 @@
         </is>
       </c>
       <c r="M598" s="5" t="n">
-        <v>2.453297</v>
+        <v>-2.453297</v>
       </c>
       <c r="N598" s="5" t="n">
         <v>1.7706</v>
@@ -68826,7 +68900,7 @@
         </is>
       </c>
       <c r="M603" s="5" t="n">
-        <v>2.453297</v>
+        <v>-2.453297</v>
       </c>
       <c r="N603" s="5" t="n">
         <v>1.7706</v>
@@ -72133,10 +72207,10 @@
         </is>
       </c>
       <c r="M636" s="5" t="n">
-        <v>2.316297</v>
+        <v>-2.316297</v>
       </c>
       <c r="N636" s="5" t="n">
-        <v>1.7656</v>
+        <v>-1.7656</v>
       </c>
       <c r="O636" t="inlineStr">
         <is>
@@ -73227,10 +73301,10 @@
         </is>
       </c>
       <c r="L647" s="5" t="n">
-        <v>2.668671</v>
+        <v>-2.668671</v>
       </c>
       <c r="M647" s="5" t="n">
-        <v>2.453297</v>
+        <v>-2.453297</v>
       </c>
       <c r="N647" t="inlineStr">
         <is>
@@ -78290,13 +78364,13 @@
         </is>
       </c>
       <c r="H698" s="5" t="n">
-        <v>8.073295</v>
+        <v>-8.073295</v>
       </c>
       <c r="I698" s="5" t="n">
-        <v>4.770078</v>
+        <v>-4.770078</v>
       </c>
       <c r="J698" s="5" t="n">
-        <v>2.274702</v>
+        <v>-2.274702</v>
       </c>
       <c r="K698" t="inlineStr">
         <is>
@@ -83782,10 +83856,10 @@
         </is>
       </c>
       <c r="E753" s="5" t="n">
-        <v>6.268738</v>
+        <v>-6.268738</v>
       </c>
       <c r="F753" s="5" t="n">
-        <v>1.207113</v>
+        <v>-1.207113</v>
       </c>
       <c r="G753" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PER.xlsx
+++ b/output/pdf_financials_xlsx/PER.xlsx
@@ -1071,16 +1071,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.051779</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002139</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01596</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004786</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02344</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.024395</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.00275</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.001135</v>
       </c>
     </row>
     <row r="13">
@@ -2019,16 +2019,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.268738</v>
+        <v>-6.216959</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>0.002139</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0.005625</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.005625</v>
+        <v>0.010335</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.24</v>
@@ -2037,10 +2037,10 @@
         <v>0.1376</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.130389</v>
+        <v>-5.125603</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.798271</v>
+        <v>2.821711</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-2.453297</v>
@@ -2061,13 +2061,13 @@
         <v>-0.94804</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.215974</v>
+        <v>-0.240369</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.074063</v>
+        <v>-0.07681300000000001</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.423684</v>
+        <v>-0.424819</v>
       </c>
     </row>
     <row r="28">
@@ -2135,16 +2135,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.268738</v>
+        <v>-6.216959</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>0.002139</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0.005625</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.005625</v>
+        <v>0.010335</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0.24</v>
@@ -2153,10 +2153,10 @@
         <v>0.1376</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.130389</v>
+        <v>-5.125603</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.798271</v>
+        <v>2.821711</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-2.453297</v>
@@ -2177,13 +2177,13 @@
         <v>-0.7072850000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.0191</v>
+        <v>-0.005295</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.131008</v>
+        <v>0.128258</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.274081</v>
+        <v>-0.275216</v>
       </c>
     </row>
     <row r="30">
@@ -2444,55 +2444,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.01009</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.772964</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.772964</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.290618</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.809122</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.068857</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>4.950363</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.497888</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.043003</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.085538</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.080162</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.048848</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.169957</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.169957</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.215956</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.107199</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.079099</v>
       </c>
     </row>
     <row r="35">
@@ -2560,55 +2560,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.01009</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.772964</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.09</v>
+        <v>0.862964</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.036</v>
+        <v>1.326618</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.03</v>
+        <v>1.839122</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.01</v>
+        <v>0.078857</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.005</v>
+        <v>4.955363</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.034311</v>
+        <v>2.532199</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.043003</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.155538</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.105162</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.048848</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.169957</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.169957</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.215956</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.107199</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.079099</v>
       </c>
     </row>
     <row r="37">
@@ -3256,55 +3256,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.024544</v>
+        <v>0.014454</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.822342</v>
+        <v>0.049378</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.732342</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.351524</v>
+        <v>0.060906</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.849741</v>
+        <v>0.040619</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.09202</v>
+        <v>0.023163</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.04933</v>
+        <v>0.098967</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.556569</v>
+        <v>0.058681</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.870506</v>
+        <v>2.827503</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.097234</v>
+        <v>0.011696</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.097043</v>
+        <v>0.016881</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.062142</v>
+        <v>0.013294</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.172236</v>
+        <v>0.002279</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.034139</v>
+        <v>0.864182</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.331649</v>
+        <v>0.115693</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.172752</v>
+        <v>0.065553</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.132415</v>
+        <v>0.053316</v>
       </c>
     </row>
     <row r="49">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -55694,7 +55694,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -66088,7 +66088,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -72765,7 +72765,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E642" s="5" t="n">
@@ -74751,7 +74751,7 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">

--- a/output/pdf_financials_xlsx/PER.xlsx
+++ b/output/pdf_financials_xlsx/PER.xlsx
@@ -1318,7 +1318,7 @@
         <v>0.24</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.1376</v>
+        <v>-2.117102</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-5.130389</v>
@@ -1376,13 +1376,13 @@
         <v>-4.972078</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-2.392302</v>
+        <v>-0.1376</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.0105</v>
+        <v>0.0105</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-5.466942</v>
+        <v>0.1296</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-6.268738</v>
+        <v>-1.359971</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-1.207113</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-4.908767</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>0.24</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.1376</v>
+        <v>-2.117102</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-5.125603</v>
@@ -2150,7 +2150,7 @@
         <v>0.24</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.1376</v>
+        <v>-2.117102</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-5.125603</v>
@@ -2302,13 +2302,13 @@
         <v>2071.699166666666</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1738.591569767442</v>
+        <v>-6.499450664162615</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0.2046628433048644</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>195.3685686625777</v>
+        <v>4.631431337422287</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -6950,22 +6950,22 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.008232</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.01178</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.012372</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.010652</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.01474</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.011792</v>
       </c>
     </row>
     <row r="111">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.044705</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -7231,31 +7231,31 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.022005</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.06611400000000001</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.02737</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0.157967</v>
+        <v>0.230759</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.17497</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.072381</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.021136</v>
       </c>
     </row>
     <row r="116">
@@ -30421,7 +30421,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -31690,7 +31694,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -33432,7 +33440,11 @@
           <t>Accretion expense (Note 11)</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -34127,7 +34139,11 @@
           <t>Proceeds on sale of investments (Note 6)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -35612,7 +35628,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -39200,7 +39220,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -43620,7 +43644,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -45452,7 +45480,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -52373,7 +52405,11 @@
           <t>Future income tax recovery (Note 6(a))</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -54086,7 +54122,11 @@
           <t>Proceeds from sale of marketable securities (Note 7)</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E455" s="5" t="n">
         <v>0.044705</v>
       </c>
@@ -73159,7 +73199,11 @@
           <t>DEFERRED INCOME TAX RECOVERY (Note 21)</t>
         </is>
       </c>
-      <c r="D646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E646" t="inlineStr">
         <is>
           <t>-</t>
@@ -74957,7 +75001,11 @@
           <t>DEFERRED INCOME TAX RECOVERY (Note 20)</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E664" t="inlineStr">
         <is>
           <t>-</t>
@@ -78244,7 +78292,11 @@
           <t>DEFERRED INCOME TAX RECOVERY (Note 17)</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E697" t="inlineStr">
         <is>
           <t>-</t>
@@ -79238,7 +79290,11 @@
           <t>DEFERRED INCOME TAX (RECOVERY) EXPENSE</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr"/>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E707" t="inlineStr">
         <is>
           <t>-</t>
@@ -83242,7 +83298,11 @@
           <t>FUTURE INCOME TAX RECOVERY (Note 6(a))</t>
         </is>
       </c>
-      <c r="D747" t="inlineStr"/>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E747" t="inlineStr">
         <is>
           <t>-</t>
@@ -83650,12 +83710,16 @@
           <t>LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D751" t="inlineStr"/>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E751" s="5" t="n">
-        <v>1.359971</v>
+        <v>-1.359971</v>
       </c>
       <c r="F751" s="5" t="n">
-        <v>1.207113</v>
+        <v>-1.207113</v>
       </c>
       <c r="G751" t="inlineStr">
         <is>
@@ -83749,9 +83813,13 @@
           <t>Loss from discontinued operations (Note 8)</t>
         </is>
       </c>
-      <c r="D752" t="inlineStr"/>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E752" s="5" t="n">
-        <v>4.908767</v>
+        <v>-4.908767</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
